--- a/消融实验.xlsx
+++ b/消融实验.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\论文\FreTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD321A6-718E-4EB1-8C81-AA7C08BD9CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F022A7A8-77AA-417C-B3AF-A8DB6AFF9B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF842CDA-56EF-42E8-BDAF-BF9DB53C1AFA}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DF842CDA-56EF-42E8-BDAF-BF9DB53C1AFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
   <si>
     <t>datasets</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -44,10 +44,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>exchange</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -91,7 +87,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ECL</t>
+    <t>ETTh1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -257,57 +253,54 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -631,656 +624,343 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
+      <c r="D1" s="14"/>
+      <c r="E1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="1"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="14"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
       <c r="E2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" t="s">
-        <v>5</v>
-      </c>
       <c r="G2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" t="s">
         <v>4</v>
-      </c>
-      <c r="H2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" t="s">
-        <v>4</v>
-      </c>
-      <c r="J2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1">
         <v>96</v>
       </c>
-      <c r="C3" s="2">
-        <v>0.34599999999999997</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.36599999999999999</v>
-      </c>
-      <c r="E3" s="2">
-        <v>9.2999999999999999E-2</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0.221</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0.21</v>
-      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>192</v>
       </c>
-      <c r="C4" s="2">
-        <v>0.38400000000000001</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0.38200000000000001</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0.16500000000000001</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0.30299999999999999</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0.245</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0.245</v>
-      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>336</v>
       </c>
-      <c r="C5" s="2">
-        <v>0.41399999999999998</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.40400000000000003</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0.30099999999999999</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0.41199999999999998</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0.28199999999999997</v>
-      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>720</v>
       </c>
-      <c r="C6" s="2">
-        <v>0.47299999999999998</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0.435</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0.58799999999999997</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.60799999999999998</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0.35699999999999998</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0.318</v>
-      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B7" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="8">
-        <v>0.40400000000000003</v>
-      </c>
-      <c r="D7" s="8">
-        <v>0.39700000000000002</v>
-      </c>
-      <c r="E7" s="8">
-        <v>0.28699999999999998</v>
-      </c>
-      <c r="F7" s="8">
-        <v>0.38600000000000001</v>
-      </c>
-      <c r="G7" s="15">
-        <v>0.27500000000000002</v>
-      </c>
-      <c r="H7" s="15">
-        <v>0.26400000000000001</v>
-      </c>
+      <c r="B7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1">
         <v>96</v>
       </c>
-      <c r="C8" s="2">
-        <v>0.33500000000000002</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0.36699999999999999</v>
-      </c>
-      <c r="E8" s="2">
-        <v>8.5999999999999993E-2</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0.21099999999999999</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0.19700000000000001</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0.20799999999999999</v>
-      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>192</v>
       </c>
-      <c r="C9" s="2">
-        <v>0.373</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0.38300000000000001</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.161</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0.29699999999999999</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0.24399999999999999</v>
-      </c>
-      <c r="H9" s="2">
-        <v>0.24399999999999999</v>
-      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <v>336</v>
       </c>
-      <c r="C10" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0.40200000000000002</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0.29499999999999998</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0.40400000000000003</v>
-      </c>
-      <c r="G10" s="2">
-        <v>0.29899999999999999</v>
-      </c>
-      <c r="H10" s="2">
-        <v>0.28000000000000003</v>
-      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <v>720</v>
       </c>
-      <c r="C11" s="2">
-        <v>0.46600000000000003</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0.436</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0.58699999999999997</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0.35799999999999998</v>
-      </c>
-      <c r="H11" s="2">
-        <v>0.318</v>
-      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B12" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="8">
-        <v>0.39400000000000002</v>
-      </c>
-      <c r="D12" s="8">
-        <v>0.39700000000000002</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.27300000000000002</v>
-      </c>
-      <c r="F12" s="8">
-        <v>0.375</v>
-      </c>
-      <c r="G12" s="16">
-        <v>0.27500000000000002</v>
-      </c>
-      <c r="H12" s="16">
-        <v>0.26200000000000001</v>
-      </c>
+      <c r="B12" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="2">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1">
         <v>96</v>
       </c>
-      <c r="C13" s="2">
-        <v>0.33600000000000002</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0.36699999999999999</v>
-      </c>
-      <c r="E13" s="2">
-        <v>8.5999999999999993E-2</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0.21099999999999999</v>
-      </c>
-      <c r="G13" s="2">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="H13" s="2">
-        <v>0.21</v>
-      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B14" s="2">
+      <c r="B14" s="1">
         <v>192</v>
       </c>
-      <c r="C14" s="2">
-        <v>0.373</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0.38300000000000001</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0.161</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0.29699999999999999</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0.245</v>
-      </c>
-      <c r="H14" s="2">
-        <v>0.245</v>
-      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B15" s="2">
+      <c r="B15" s="1">
         <v>336</v>
       </c>
-      <c r="C15" s="2">
-        <v>0.40200000000000002</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0.40300000000000002</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0.29299999999999998</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0.40300000000000002</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="H15" s="2">
-        <v>0.28100000000000003</v>
-      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B16" s="2">
+      <c r="B16" s="1">
         <v>720</v>
       </c>
-      <c r="C16" s="2">
-        <v>0.46600000000000003</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0.436</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0.58599999999999997</v>
-      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B17" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="8">
-        <v>0.39400000000000002</v>
-      </c>
-      <c r="D17" s="8">
-        <v>0.39700000000000002</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.27200000000000002</v>
-      </c>
-      <c r="F17" s="8">
-        <v>0.374</v>
-      </c>
+      <c r="B17" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="3">
+        <v>11</v>
+      </c>
+      <c r="B18" s="1">
         <v>96</v>
       </c>
-      <c r="C18" s="3">
-        <v>0.33700000000000002</v>
-      </c>
-      <c r="D18" s="3">
-        <v>0.36799999999999999</v>
-      </c>
-      <c r="E18" s="3">
-        <v>8.5999999999999993E-2</v>
-      </c>
-      <c r="F18" s="3">
-        <v>0.21199999999999999</v>
-      </c>
-      <c r="G18" s="3">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="H18" s="3">
-        <v>0.21</v>
-      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B19" s="3">
+      <c r="B19" s="1">
         <v>192</v>
       </c>
-      <c r="C19" s="3">
-        <v>0.373</v>
-      </c>
-      <c r="D19" s="3">
-        <v>0.38300000000000001</v>
-      </c>
-      <c r="E19" s="3">
-        <v>0.161</v>
-      </c>
-      <c r="F19" s="3">
-        <v>0.29699999999999999</v>
-      </c>
-      <c r="G19" s="3">
-        <v>0.245</v>
-      </c>
-      <c r="H19" s="3">
-        <v>0.245</v>
-      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B20" s="3">
+      <c r="B20" s="1">
         <v>336</v>
       </c>
-      <c r="C20" s="3">
-        <v>0.40300000000000002</v>
-      </c>
-      <c r="D20" s="3">
-        <v>0.40300000000000002</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0.29399999999999998</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0.40400000000000003</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0.28100000000000003</v>
-      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B21" s="3">
+      <c r="B21" s="1">
         <v>720</v>
       </c>
-      <c r="C21" s="3">
-        <v>0.46700000000000003</v>
-      </c>
-      <c r="D21" s="3">
-        <v>0.437</v>
-      </c>
-      <c r="E21" s="3">
-        <v>0.55100000000000005</v>
-      </c>
-      <c r="F21" s="3">
-        <v>0.58799999999999997</v>
-      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B22" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="9">
-        <v>0.39500000000000002</v>
-      </c>
-      <c r="D22" s="9">
-        <v>0.39800000000000002</v>
-      </c>
-      <c r="E22" s="9">
-        <v>0.27300000000000002</v>
-      </c>
-      <c r="F22" s="9">
-        <v>0.375</v>
-      </c>
+      <c r="B22" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="2">
+        <v>8</v>
+      </c>
+      <c r="B23" s="1">
         <v>96</v>
       </c>
-      <c r="C23" s="6">
-        <v>0.32400000000000001</v>
-      </c>
-      <c r="D23" s="7">
-        <v>0.36099999999999999</v>
-      </c>
-      <c r="E23" s="6">
-        <v>8.5000000000000006E-2</v>
-      </c>
-      <c r="F23" s="7">
-        <v>0.21099999999999999</v>
-      </c>
-      <c r="G23" s="6">
-        <v>0.17</v>
-      </c>
-      <c r="H23" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="I23" s="6">
-        <v>0.152</v>
-      </c>
-      <c r="J23" s="7">
-        <v>0.247</v>
-      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="5"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B24" s="2">
+      <c r="B24" s="1">
         <v>192</v>
       </c>
-      <c r="C24" s="4">
-        <v>0.374</v>
-      </c>
-      <c r="D24" s="5">
-        <v>0.38300000000000001</v>
-      </c>
-      <c r="E24" s="4">
-        <v>0.16</v>
-      </c>
-      <c r="F24" s="5">
-        <v>0.29699999999999999</v>
-      </c>
-      <c r="G24" s="4">
-        <v>0.22500000000000001</v>
-      </c>
-      <c r="H24" s="5">
-        <v>0.24199999999999999</v>
-      </c>
-      <c r="I24" s="4">
-        <v>0.158</v>
-      </c>
-      <c r="J24" s="5">
-        <v>0.253</v>
-      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="3"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B25" s="2">
+      <c r="B25" s="1">
         <v>336</v>
       </c>
-      <c r="C25" s="4">
-        <v>0.39600000000000002</v>
-      </c>
-      <c r="D25" s="5">
-        <v>0.39700000000000002</v>
-      </c>
-      <c r="E25" s="4">
-        <v>0.29499999999999998</v>
-      </c>
-      <c r="F25" s="5">
-        <v>0.40400000000000003</v>
-      </c>
-      <c r="G25" s="4">
-        <v>0.28100000000000003</v>
-      </c>
-      <c r="H25" s="5">
-        <v>0.27600000000000002</v>
-      </c>
-      <c r="I25" s="4">
-        <v>0.17199999999999999</v>
-      </c>
-      <c r="J25" s="5">
-        <v>0.27200000000000002</v>
-      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="3"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B26" s="2">
+      <c r="B26" s="1">
         <v>720</v>
       </c>
-      <c r="C26" s="4">
-        <v>0.46100000000000002</v>
-      </c>
-      <c r="D26" s="5">
-        <v>0.44</v>
-      </c>
-      <c r="E26" s="4">
-        <v>0.54800000000000004</v>
-      </c>
-      <c r="F26" s="5">
-        <v>0.58599999999999997</v>
-      </c>
-      <c r="G26" s="4">
-        <v>0.34399999999999997</v>
-      </c>
-      <c r="H26" s="5">
-        <v>0.312</v>
-      </c>
-      <c r="I26" s="4">
-        <v>0.18099999999999999</v>
-      </c>
-      <c r="J26" s="5">
-        <v>0.28000000000000003</v>
-      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="3"/>
     </row>
     <row r="27" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="11">
-        <v>0.38800000000000001</v>
-      </c>
-      <c r="D27" s="12">
-        <v>0.39500000000000002</v>
-      </c>
-      <c r="E27" s="11">
-        <v>0.27200000000000002</v>
-      </c>
-      <c r="F27" s="12">
-        <v>0.374</v>
-      </c>
-      <c r="G27" s="13">
-        <v>0.255</v>
-      </c>
-      <c r="H27" s="14">
-        <v>0.25700000000000001</v>
-      </c>
-      <c r="I27" s="13">
-        <v>0.16500000000000001</v>
-      </c>
-      <c r="J27" s="14">
-        <v>0.26300000000000001</v>
-      </c>
+      <c r="B27" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/消融实验.xlsx
+++ b/消融实验.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\论文\FreTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F022A7A8-77AA-417C-B3AF-A8DB6AFF9B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B18F0BE-68AC-460B-A9A8-3981CEAF2E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DF842CDA-56EF-42E8-BDAF-BF9DB53C1AFA}"/>
   </bookViews>
@@ -126,27 +126,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -193,17 +181,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -247,60 +224,118 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -623,44 +658,45 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14" t="s">
+      <c r="D1" s="17"/>
+      <c r="E1" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14" t="s">
+      <c r="F1" s="17"/>
+      <c r="G1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="14"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2" s="22"/>
+      <c r="C2" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="19" t="s">
         <v>4</v>
       </c>
     </row>
@@ -668,293 +704,606 @@
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="23">
         <v>96</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
+      <c r="C3" s="23">
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="D3" s="19">
+        <v>0.36299999999999999</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.372</v>
+      </c>
+      <c r="F3" s="19">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="G3" s="18">
+        <v>0.152</v>
+      </c>
+      <c r="H3" s="19">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B4" s="1">
+      <c r="B4" s="23">
         <v>192</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
+      <c r="C4" s="23">
+        <v>0.36199999999999999</v>
+      </c>
+      <c r="D4" s="19">
+        <v>0.38</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="F4" s="19">
+        <v>0.42199999999999999</v>
+      </c>
+      <c r="G4" s="18">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="H4" s="19">
+        <v>0.247</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B5" s="1">
+      <c r="B5" s="23">
         <v>336</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
+      <c r="C5" s="23">
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="D5" s="19">
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.47599999999999998</v>
+      </c>
+      <c r="F5" s="19">
+        <v>0.443</v>
+      </c>
+      <c r="G5" s="18">
+        <v>0.26300000000000001</v>
+      </c>
+      <c r="H5" s="19">
+        <v>0.29199999999999998</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B6" s="1">
+      <c r="B6" s="23">
         <v>720</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
+      <c r="C6" s="23">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="D6" s="19">
+        <v>0.441</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.498</v>
+      </c>
+      <c r="F6" s="19">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="G6" s="18">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="H6" s="19">
+        <v>0.34100000000000003</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B7" s="6" t="s">
+      <c r="A7" s="26"/>
+      <c r="B7" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
+      <c r="C7" s="24">
+        <v>0.39</v>
+      </c>
+      <c r="D7" s="11">
+        <v>0.39700000000000002</v>
+      </c>
+      <c r="E7" s="8">
+        <v>0.443</v>
+      </c>
+      <c r="F7" s="11">
+        <v>0.432</v>
+      </c>
+      <c r="G7" s="15">
+        <v>0.24</v>
+      </c>
+      <c r="H7" s="20">
+        <v>0.27</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="5">
         <v>96</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
+      <c r="C8" s="5">
+        <v>0.317</v>
+      </c>
+      <c r="D8" s="10">
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="F8" s="10">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="G8" s="12">
+        <v>0.154</v>
+      </c>
+      <c r="H8" s="10">
+        <v>0.19900000000000001</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B9" s="1">
+      <c r="B9" s="5">
         <v>192</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
+      <c r="C9" s="5">
+        <v>0.36299999999999999</v>
+      </c>
+      <c r="D9" s="10">
+        <v>0.379</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0.434</v>
+      </c>
+      <c r="F9" s="10">
+        <v>0.42299999999999999</v>
+      </c>
+      <c r="G9" s="12">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="H9" s="10">
+        <v>0.247</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B10" s="1">
+      <c r="B10" s="5">
         <v>336</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
+      <c r="C10" s="5">
+        <v>0.39700000000000002</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="F10" s="10">
+        <v>0.441</v>
+      </c>
+      <c r="G10" s="12">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="H10" s="10">
+        <v>0.29199999999999998</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B11" s="1">
+      <c r="B11" s="5">
         <v>720</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
+      <c r="C11" s="5">
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="D11" s="10">
+        <v>0.44</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="F11" s="10">
+        <v>0.47</v>
+      </c>
+      <c r="G11" s="12">
+        <v>0.34200000000000003</v>
+      </c>
+      <c r="H11" s="10">
+        <v>0.34200000000000003</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B12" s="6" t="s">
+      <c r="A12" s="26"/>
+      <c r="B12" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
+      <c r="C12" s="24">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="D12" s="11">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="F12" s="11">
+        <v>0.432</v>
+      </c>
+      <c r="G12" s="8">
+        <v>0.24099999999999999</v>
+      </c>
+      <c r="H12" s="11">
+        <v>0.27</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="5">
         <v>96</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
+      <c r="C13" s="5">
+        <v>0.31900000000000001</v>
+      </c>
+      <c r="D13" s="10">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="E13" s="4">
+        <v>0.38100000000000001</v>
+      </c>
+      <c r="F13" s="10">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="H13" s="10">
+        <v>0.21</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B14" s="1">
+      <c r="B14" s="5">
         <v>192</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
+      <c r="C14" s="5">
+        <v>0.36599999999999999</v>
+      </c>
+      <c r="D14" s="10">
+        <v>0.38100000000000001</v>
+      </c>
+      <c r="E14" s="4">
+        <v>0.436</v>
+      </c>
+      <c r="F14" s="10">
+        <v>0.42399999999999999</v>
+      </c>
+      <c r="G14" s="12">
+        <v>0.20899999999999999</v>
+      </c>
+      <c r="H14" s="10">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B15" s="1">
+      <c r="B15" s="5">
         <v>336</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
+      <c r="C15" s="5">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="D15" s="10">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="F15" s="10">
+        <v>0.442</v>
+      </c>
+      <c r="G15" s="12">
+        <v>0.26600000000000001</v>
+      </c>
+      <c r="H15" s="10">
+        <v>0.29199999999999998</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B16" s="1">
+      <c r="B16" s="5">
         <v>720</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="C16" s="5">
+        <v>0.47699999999999998</v>
+      </c>
+      <c r="D16" s="10">
+        <v>0.439</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="F16" s="10">
+        <v>0.47</v>
+      </c>
+      <c r="G16" s="12">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="H16" s="10">
+        <v>0.34499999999999997</v>
+      </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B17" s="6" t="s">
+      <c r="A17" s="26"/>
+      <c r="B17" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
+      <c r="C17" s="24">
+        <v>0.39</v>
+      </c>
+      <c r="D17" s="11">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="F17" s="11">
+        <v>0.433</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0.246</v>
+      </c>
+      <c r="H17" s="11">
+        <v>0.27400000000000002</v>
+      </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="5">
         <v>96</v>
       </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
+      <c r="C18" s="5">
+        <v>0.32</v>
+      </c>
+      <c r="D18" s="10">
+        <v>0.35799999999999998</v>
+      </c>
+      <c r="E18" s="4">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="F18" s="10">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="G18" s="12">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="H18" s="10">
+        <v>0.20899999999999999</v>
+      </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B19" s="1">
+      <c r="B19" s="5">
         <v>192</v>
       </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
+      <c r="C19" s="5">
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="D19" s="10">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="E19" s="4">
+        <v>0.434</v>
+      </c>
+      <c r="F19" s="10">
+        <v>0.42299999999999999</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="H19" s="10">
+        <v>0.251</v>
+      </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B20" s="1">
+      <c r="B20" s="5">
         <v>336</v>
       </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
+      <c r="C20" s="5">
+        <v>0.40100000000000002</v>
+      </c>
+      <c r="D20" s="10">
+        <v>0.40600000000000003</v>
+      </c>
+      <c r="E20" s="4">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="F20" s="10">
+        <v>0.442</v>
+      </c>
+      <c r="G20" s="12">
+        <v>0.26800000000000002</v>
+      </c>
+      <c r="H20" s="10">
+        <v>0.29199999999999998</v>
+      </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B21" s="1">
+      <c r="B21" s="5">
         <v>720</v>
       </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
+      <c r="C21" s="5">
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="D21" s="10">
+        <v>0.439</v>
+      </c>
+      <c r="E21" s="4">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="F21" s="10">
+        <v>0.47</v>
+      </c>
+      <c r="G21" s="12">
+        <v>0.34399999999999997</v>
+      </c>
+      <c r="H21" s="10">
+        <v>0.34300000000000003</v>
+      </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B22" s="6" t="s">
+      <c r="A22" s="26"/>
+      <c r="B22" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
+      <c r="C22" s="24">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="D22" s="11">
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="E22" s="4">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="F22" s="11">
+        <v>0.433</v>
+      </c>
+      <c r="G22" s="8">
+        <v>0.248</v>
+      </c>
+      <c r="H22" s="11">
+        <v>0.27400000000000002</v>
+      </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="23">
         <v>96</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="5"/>
+      <c r="C23" s="3">
+        <v>0.313</v>
+      </c>
+      <c r="D23" s="9">
+        <v>0.35</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0.38</v>
+      </c>
+      <c r="F23" s="9">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0.153</v>
+      </c>
+      <c r="H23" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B24" s="1">
+      <c r="B24" s="23">
         <v>192</v>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="3"/>
+      <c r="C24" s="5">
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0.38</v>
+      </c>
+      <c r="E24" s="5">
+        <v>0.434</v>
+      </c>
+      <c r="F24" s="4">
+        <v>0.42299999999999999</v>
+      </c>
+      <c r="G24" s="5">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="H24" s="10">
+        <v>0.247</v>
+      </c>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B25" s="1">
+      <c r="B25" s="23">
         <v>336</v>
       </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="3"/>
+      <c r="C25" s="5">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0.40200000000000002</v>
+      </c>
+      <c r="E25" s="5">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="F25" s="4">
+        <v>0.441</v>
+      </c>
+      <c r="G25" s="5">
+        <v>0.26200000000000001</v>
+      </c>
+      <c r="H25" s="10">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B26" s="1">
+      <c r="B26" s="23">
         <v>720</v>
       </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="3"/>
+      <c r="C26" s="5">
+        <v>0.47</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="E26" s="5">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="F26" s="4">
+        <v>0.47</v>
+      </c>
+      <c r="G26" s="5">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="H26" s="10">
+        <v>0.34399999999999997</v>
+      </c>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
     </row>
     <row r="27" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="8" t="s">
+      <c r="A27" s="21"/>
+      <c r="B27" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="9"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="12"/>
+      <c r="C27" s="6">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="D27" s="7">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="F27" s="7">
+        <v>0.432</v>
+      </c>
+      <c r="G27" s="6">
+        <v>0.24</v>
+      </c>
+      <c r="H27" s="11">
+        <v>0.27</v>
+      </c>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="3">
